--- a/Papers/STM32H563ZIT6/NUCLEO_H563ZI_Final_Pinout.xlsx
+++ b/Papers/STM32H563ZIT6/NUCLEO_H563ZI_Final_Pinout.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xavi\Documents\UOC\DDR5_Test_Platform_XR\Papers\STM32H563ZIT6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xavier.rocher\Documents\Projects\DDR5_Test_Platform_XR\Papers\STM32H563ZIT6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14E8678-A15D-4997-B8AF-3BC90699882B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF88F09A-D087-4354-B575-C2B343597E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NUCLEO_H563ZI_Pinout" sheetId="1" r:id="rId1"/>
@@ -207,15 +207,9 @@
     <t>EN_6</t>
   </si>
   <si>
-    <t>PD6</t>
-  </si>
-  <si>
     <t>EN_7</t>
   </si>
   <si>
-    <t>PD7</t>
-  </si>
-  <si>
     <t>PWR_GOOD_RDIMM</t>
   </si>
   <si>
@@ -457,6 +451,12 @@
   </si>
   <si>
     <t>USB_PD</t>
+  </si>
+  <si>
+    <t>PC7</t>
+  </si>
+  <si>
+    <t>PC8</t>
   </si>
 </sst>
 </file>
@@ -578,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -586,10 +586,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -598,7 +595,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -608,19 +611,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -645,22 +636,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>40821</xdr:colOff>
+      <xdr:colOff>247650</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>54428</xdr:rowOff>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>68035</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>158853</xdr:rowOff>
+      <xdr:colOff>68181</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>39604</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imatge 2">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2AC3B50-8702-9702-5249-33DCF4A7BA0E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D64E110-0F40-4BC5-0F5D-D4C2901E6294}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -676,8 +667,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9103178" y="54428"/>
-          <a:ext cx="11049000" cy="9819925"/>
+          <a:off x="9534525" y="123825"/>
+          <a:ext cx="10793331" cy="10774279"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -718,7 +709,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="68527" y="31614"/>
-          <a:ext cx="3414959" cy="4272352"/>
+          <a:ext cx="3443430" cy="4272352"/>
           <a:chOff x="4063074" y="7801"/>
           <a:chExt cx="3414959" cy="4272352"/>
         </a:xfrm>
@@ -976,10 +967,10 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="5854625" y="1642613"/>
-            <a:ext cx="857126" cy="331632"/>
-            <a:chOff x="5860383" y="996854"/>
-            <a:chExt cx="865855" cy="331632"/>
+            <a:off x="5822453" y="1605164"/>
+            <a:ext cx="889295" cy="110289"/>
+            <a:chOff x="5827886" y="959405"/>
+            <a:chExt cx="898352" cy="110289"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:cxnSp macro="">
@@ -991,12 +982,14 @@
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
-            <xdr:cNvCxnSpPr/>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="15" idx="3"/>
+            </xdr:cNvCxnSpPr>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
             <a:xfrm flipV="1">
-              <a:off x="6311566" y="996854"/>
-              <a:ext cx="414672" cy="281502"/>
+              <a:off x="6279070" y="996854"/>
+              <a:ext cx="447168" cy="17696"/>
             </a:xfrm>
             <a:prstGeom prst="straightConnector1">
               <a:avLst/>
@@ -1033,7 +1026,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5860383" y="1218197"/>
+              <a:off x="5827886" y="959405"/>
               <a:ext cx="451184" cy="110289"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4389,6 +4382,240 @@
         </xdr:sp>
       </xdr:grpSp>
     </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>452859</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>32349</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>284292</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>107748</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Connector de fletxa recta 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5077E217-140A-4351-9DE7-1EB57FE680FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2285972" y="1746849"/>
+          <a:ext cx="442471" cy="75399"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3595</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>47589</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>452860</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>157878</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="QuadreDeText 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6598FA27-66EB-4D7D-B08F-14D45256D2CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1836708" y="1762089"/>
+          <a:ext cx="449265" cy="110289"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="9525"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="500" b="1"/>
+            <a:t>PC7</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>397144</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>43916</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>93283</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>83949</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="Connector de fletxa recta 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB2090CF-B2DE-4D1B-A890-E6305EF1CC97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2838127" y="996416"/>
+          <a:ext cx="306385" cy="40033"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>93283</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>174356</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>428096</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>103975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="QuadreDeText 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0D20C13-CADD-45F4-8BEC-ABD8E9A69D13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3144512" y="936356"/>
+          <a:ext cx="334813" cy="120119"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="9525"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="500" b="1"/>
+            <a:t>PC8</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4739,24 +4966,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -4769,7 +4996,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -4777,7 +5004,7 @@
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -4790,7 +5017,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -4798,7 +5025,7 @@
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -4817,7 +5044,7 @@
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -4836,7 +5063,7 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -4857,7 +5084,7 @@
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -4876,7 +5103,7 @@
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -4895,7 +5122,7 @@
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -4914,7 +5141,7 @@
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -4933,7 +5160,7 @@
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -4952,7 +5179,7 @@
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -4971,7 +5198,7 @@
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -4992,7 +5219,7 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -5013,7 +5240,7 @@
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -5032,7 +5259,7 @@
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -5051,7 +5278,7 @@
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -5070,7 +5297,7 @@
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -5089,7 +5316,7 @@
       <c r="I18" s="1"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -5106,17 +5333,17 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="8"/>
+      <c r="J19" s="7"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>48</v>
@@ -5128,14 +5355,14 @@
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>63</v>
+        <v>144</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>48</v>
@@ -5147,36 +5374,36 @@
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="9"/>
+      <c r="E22" s="8"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
-        <v>64</v>
+      <c r="A23" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="1"/>
@@ -5185,17 +5412,17 @@
       <c r="I23" s="1"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>64</v>
+      <c r="A24" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="1"/>
@@ -5204,17 +5431,17 @@
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
-        <v>64</v>
+      <c r="A25" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="1"/>
@@ -5223,17 +5450,17 @@
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>64</v>
+      <c r="A26" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="1"/>
@@ -5242,17 +5469,17 @@
       <c r="I26" s="1"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
-        <v>64</v>
+      <c r="A27" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="1"/>
@@ -5261,17 +5488,17 @@
       <c r="I27" s="1"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
-        <v>64</v>
+      <c r="A28" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="1"/>
@@ -5280,17 +5507,17 @@
       <c r="I28" s="1"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
-        <v>64</v>
+      <c r="A29" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="1"/>
@@ -5299,20 +5526,20 @@
       <c r="I29" s="1"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="E30" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -5320,20 +5547,20 @@
       <c r="I30" s="1"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>82</v>
+      <c r="A31" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -5341,20 +5568,20 @@
       <c r="I31" s="1"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="E32" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -5362,20 +5589,20 @@
       <c r="I32" s="1"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>89</v>
+      <c r="A33" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -5383,20 +5610,20 @@
       <c r="I33" s="1"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
-        <v>89</v>
+      <c r="A34" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -5404,20 +5631,20 @@
       <c r="I34" s="1"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
-        <v>89</v>
+      <c r="A35" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -5425,20 +5652,20 @@
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="E36" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -5446,20 +5673,20 @@
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
-        <v>103</v>
+      <c r="A37" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -5467,48 +5694,48 @@
       <c r="I37" s="1"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
+      <c r="A38" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="17"/>
-      <c r="B39" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
+      <c r="A39" s="10"/>
+      <c r="B39" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="7" t="s">
-        <v>115</v>
+      <c r="A40" s="10"/>
+      <c r="B40" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D40" s="5"/>
+      <c r="E40" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -5516,16 +5743,16 @@
       <c r="I40" s="1"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="17"/>
-      <c r="B41" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D41" s="6"/>
-      <c r="E41" s="7" t="s">
-        <v>114</v>
+      <c r="A41" s="10"/>
+      <c r="B41" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" s="5"/>
+      <c r="E41" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -5565,13 +5792,13 @@
       <c r="I44" s="1"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B45" s="13" t="s">
+      <c r="A45" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="14"/>
+      <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -5581,13 +5808,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>139</v>
+      <c r="C46" s="11" t="s">
+        <v>137</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -5598,12 +5825,12 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C47" s="11"/>
+      <c r="C47" s="12"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -5613,12 +5840,12 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C48" s="11"/>
+        <v>123</v>
+      </c>
+      <c r="C48" s="12"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -5628,12 +5855,12 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C49" s="11"/>
+        <v>124</v>
+      </c>
+      <c r="C49" s="12"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -5643,12 +5870,12 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C50" s="11"/>
+        <v>125</v>
+      </c>
+      <c r="C50" s="12"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -5658,62 +5885,62 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C51" s="11"/>
+        <v>126</v>
+      </c>
+      <c r="C51" s="12"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C52" s="11"/>
+        <v>127</v>
+      </c>
+      <c r="C52" s="12"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C53" s="11"/>
+        <v>128</v>
+      </c>
+      <c r="C53" s="12"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="13"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C54" s="12"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="15" t="s">
+      <c r="B55" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B55" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C56" s="4"/>
+      <c r="C56" s="14"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D58" s="8"/>
+      <c r="D58" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5738,16 +5965,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -5759,10 +5986,10 @@
         <v>7</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="7:11" x14ac:dyDescent="0.25">
@@ -5773,10 +6000,10 @@
         <v>10</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="7:11" x14ac:dyDescent="0.25">
@@ -5787,10 +6014,10 @@
         <v>13</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="7:11" x14ac:dyDescent="0.25">
@@ -5801,10 +6028,10 @@
         <v>16</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="7:11" x14ac:dyDescent="0.25">
@@ -5815,10 +6042,10 @@
         <v>19</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="7:11" x14ac:dyDescent="0.25">
@@ -5829,10 +6056,10 @@
         <v>23</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="7:11" x14ac:dyDescent="0.25">
@@ -5843,10 +6070,10 @@
         <v>26</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="7:11" x14ac:dyDescent="0.25">
@@ -5857,10 +6084,10 @@
         <v>29</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="7:11" x14ac:dyDescent="0.25">
@@ -5871,10 +6098,10 @@
         <v>32</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="7:11" x14ac:dyDescent="0.25">
@@ -5885,10 +6112,10 @@
         <v>35</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="7:11" x14ac:dyDescent="0.25">
@@ -5899,10 +6126,10 @@
         <v>39</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="7:11" x14ac:dyDescent="0.25">
@@ -5913,10 +6140,10 @@
         <v>42</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="7:11" x14ac:dyDescent="0.25">
@@ -5927,10 +6154,10 @@
         <v>47</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="7:11" x14ac:dyDescent="0.25">
@@ -5941,10 +6168,10 @@
         <v>51</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="7:14" x14ac:dyDescent="0.25">
@@ -5954,7 +6181,7 @@
       <c r="H17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="N17" s="8"/>
+      <c r="N17" s="7"/>
     </row>
     <row r="18" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G18" s="2" t="s">
@@ -5985,15 +6212,15 @@
         <v>60</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G22" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>63</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Papers/STM32H563ZIT6/NUCLEO_H563ZI_Final_Pinout.xlsx
+++ b/Papers/STM32H563ZIT6/NUCLEO_H563ZI_Final_Pinout.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xavier.rocher\Documents\Projects\DDR5_Test_Platform_XR\Papers\STM32H563ZIT6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xavi\Documents\UOC\DDR5_Test_Platform_XR\Papers\STM32H563ZIT6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF88F09A-D087-4354-B575-C2B343597E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136D9047-DE86-4C51-B8C5-14E08DC7A68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NUCLEO_H563ZI_Pinout" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="153">
   <si>
     <t>Category</t>
   </si>
@@ -457,6 +457,30 @@
   </si>
   <si>
     <t>PC8</t>
+  </si>
+  <si>
+    <t>LED_STATUS_0</t>
+  </si>
+  <si>
+    <t>LED_STATUS_1</t>
+  </si>
+  <si>
+    <t>LED_STATUS_2</t>
+  </si>
+  <si>
+    <t>LED_STATUS_3</t>
+  </si>
+  <si>
+    <t>PC10</t>
+  </si>
+  <si>
+    <t>PC11</t>
+  </si>
+  <si>
+    <t>PC12</t>
+  </si>
+  <si>
+    <t>PF7</t>
   </si>
 </sst>
 </file>
@@ -488,7 +512,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -510,6 +534,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,7 +608,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -613,6 +643,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -709,7 +745,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="68527" y="31614"/>
-          <a:ext cx="3443430" cy="4272352"/>
+          <a:ext cx="3419538" cy="4272352"/>
           <a:chOff x="4063074" y="7801"/>
           <a:chExt cx="3414959" cy="4272352"/>
         </a:xfrm>
@@ -5964,7 +6000,7 @@
     <col min="11" max="11" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="7:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="7:13" x14ac:dyDescent="0.25">
       <c r="G2" s="4" t="s">
         <v>1</v>
       </c>
@@ -5978,237 +6014,262 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G3" s="2" t="s">
+    <row r="3" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="15" t="s">
         <v>63</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G4" s="2" t="s">
+    <row r="4" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="G4" s="15" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="15" t="s">
         <v>66</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G5" s="2" t="s">
+    <row r="5" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="G5" s="15" t="s">
         <v>12</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="15" t="s">
         <v>68</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G6" s="2" t="s">
+    <row r="6" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="G6" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="15" t="s">
         <v>70</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G7" s="2" t="s">
+    <row r="7" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="G7" s="15" t="s">
         <v>18</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="15" t="s">
         <v>72</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G8" s="2" t="s">
+    <row r="8" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="G8" s="15" t="s">
         <v>22</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="15" t="s">
         <v>74</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G9" s="2" t="s">
+    <row r="9" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="G9" s="15" t="s">
         <v>25</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="15" t="s">
         <v>76</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G10" s="2" t="s">
+    <row r="10" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="G10" s="15" t="s">
         <v>28</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="15" t="s">
         <v>78</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G11" s="2" t="s">
+    <row r="11" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="G11" s="15" t="s">
         <v>31</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="15" t="s">
         <v>81</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G12" s="2" t="s">
+    <row r="12" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="G12" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="15" t="s">
         <v>85</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G13" s="2" t="s">
+    <row r="13" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="G13" s="15" t="s">
         <v>38</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="15" t="s">
         <v>88</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G14" s="2" t="s">
+    <row r="14" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="G14" s="15" t="s">
         <v>41</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="15" t="s">
         <v>92</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G15" s="2" t="s">
+    <row r="15" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="G15" s="15" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" s="15" t="s">
         <v>95</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="7:11" x14ac:dyDescent="0.25">
-      <c r="G16" s="2" t="s">
+    <row r="16" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="G16" s="15" t="s">
         <v>50</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" s="15" t="s">
         <v>98</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="M16" s="7"/>
     </row>
     <row r="17" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="15" t="s">
         <v>52</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="J17" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="N17" s="7"/>
     </row>
     <row r="18" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="15" t="s">
         <v>54</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="J18" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="19" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="15" t="s">
         <v>56</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="J19" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="20" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="15" t="s">
         <v>58</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="J20" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="21" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="15" t="s">
         <v>60</v>
       </c>
       <c r="H21" s="2" t="s">
@@ -6216,7 +6277,7 @@
       </c>
     </row>
     <row r="22" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="15" t="s">
         <v>61</v>
       </c>
       <c r="H22" s="2" t="s">

--- a/Papers/STM32H563ZIT6/NUCLEO_H563ZI_Final_Pinout.xlsx
+++ b/Papers/STM32H563ZIT6/NUCLEO_H563ZI_Final_Pinout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xavi\Documents\UOC\DDR5_Test_Platform_XR\Papers\STM32H563ZIT6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136D9047-DE86-4C51-B8C5-14E08DC7A68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43AA738-60B1-45A1-BF59-D63789978F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NUCLEO_H563ZI_Pinout" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="161">
   <si>
     <t>Category</t>
   </si>
@@ -481,6 +481,30 @@
   </si>
   <si>
     <t>PF7</t>
+  </si>
+  <si>
+    <t>LED_STATUS_0 ( PASS)</t>
+  </si>
+  <si>
+    <t>LED_STATUS_1 (FAIL)</t>
+  </si>
+  <si>
+    <t>LED_STATUS_2 (RUN)</t>
+  </si>
+  <si>
+    <t>LED_STATUS_3 (STOP)</t>
+  </si>
+  <si>
+    <t>LED_PASS_TEST</t>
+  </si>
+  <si>
+    <t>LED_FAIL_TEST</t>
+  </si>
+  <si>
+    <t>LED_RUNNING_TEST</t>
+  </si>
+  <si>
+    <t>LED_STOP_TEST</t>
   </si>
 </sst>
 </file>
@@ -629,9 +653,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -647,8 +668,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4991,7 +5015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.5703125" customWidth="1"/>
@@ -5730,173 +5754,169 @@
       <c r="I37" s="1"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
+      <c r="A38" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="3"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-      <c r="B39" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
+      <c r="A39" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="3"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D40" s="5"/>
-      <c r="E40" s="6" t="s">
-        <v>113</v>
-      </c>
+      <c r="A40" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" s="3"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-      <c r="B41" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D41" s="5"/>
-      <c r="E41" s="6" t="s">
-        <v>112</v>
-      </c>
+      <c r="A41" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" s="3"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
+      <c r="E44" s="7"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
+      <c r="A45" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
+      <c r="A46" s="15"/>
+      <c r="B46" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" s="12"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
+      <c r="A47" s="15"/>
+      <c r="B47" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D47" s="5"/>
+      <c r="E47" s="6" t="s">
+        <v>113</v>
+      </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C48" s="12"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
+      <c r="A48" s="15"/>
+      <c r="B48" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D48" s="5"/>
+      <c r="E48" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C49" s="12"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -5905,13 +5925,9 @@
       <c r="I49" s="1"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C50" s="12"/>
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -5920,69 +5936,142 @@
       <c r="I50" s="1"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C51" s="12"/>
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C52" s="12"/>
+      <c r="A52" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C53" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C54" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="C54" s="11"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>142</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="C55" s="11"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C56" s="11"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" s="11"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C58" s="11"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C59" s="11"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C60" s="11"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C61" s="12"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B63" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C56" s="14"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D58" s="7"/>
+      <c r="C63" s="13"/>
+    </row>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D65" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="C46:C54"/>
-    <mergeCell ref="C55:C56"/>
+  <mergeCells count="1">
+    <mergeCell ref="A45:A48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6015,13 +6104,13 @@
       </c>
     </row>
     <row r="3" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="14" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="14" t="s">
         <v>63</v>
       </c>
       <c r="K3" s="2" t="s">
@@ -6029,13 +6118,13 @@
       </c>
     </row>
     <row r="4" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="14" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="14" t="s">
         <v>66</v>
       </c>
       <c r="K4" s="2" t="s">
@@ -6043,13 +6132,13 @@
       </c>
     </row>
     <row r="5" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>12</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>68</v>
       </c>
       <c r="K5" s="2" t="s">
@@ -6057,13 +6146,13 @@
       </c>
     </row>
     <row r="6" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="14" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="14" t="s">
         <v>70</v>
       </c>
       <c r="K6" s="2" t="s">
@@ -6071,13 +6160,13 @@
       </c>
     </row>
     <row r="7" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>18</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="14" t="s">
         <v>72</v>
       </c>
       <c r="K7" s="2" t="s">
@@ -6085,13 +6174,13 @@
       </c>
     </row>
     <row r="8" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="14" t="s">
         <v>22</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="14" t="s">
         <v>74</v>
       </c>
       <c r="K8" s="2" t="s">
@@ -6099,13 +6188,13 @@
       </c>
     </row>
     <row r="9" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>25</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="14" t="s">
         <v>76</v>
       </c>
       <c r="K9" s="2" t="s">
@@ -6113,13 +6202,13 @@
       </c>
     </row>
     <row r="10" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="14" t="s">
         <v>28</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="14" t="s">
         <v>78</v>
       </c>
       <c r="K10" s="2" t="s">
@@ -6127,13 +6216,13 @@
       </c>
     </row>
     <row r="11" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>31</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="14" t="s">
         <v>81</v>
       </c>
       <c r="K11" s="2" t="s">
@@ -6141,13 +6230,13 @@
       </c>
     </row>
     <row r="12" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="14" t="s">
         <v>85</v>
       </c>
       <c r="K12" s="2" t="s">
@@ -6155,13 +6244,13 @@
       </c>
     </row>
     <row r="13" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="14" t="s">
         <v>38</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="14" t="s">
         <v>88</v>
       </c>
       <c r="K13" s="2" t="s">
@@ -6169,13 +6258,13 @@
       </c>
     </row>
     <row r="14" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="14" t="s">
         <v>41</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="J14" s="14" t="s">
         <v>92</v>
       </c>
       <c r="K14" s="2" t="s">
@@ -6183,13 +6272,13 @@
       </c>
     </row>
     <row r="15" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="14" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="14" t="s">
         <v>95</v>
       </c>
       <c r="K15" s="2" t="s">
@@ -6197,13 +6286,13 @@
       </c>
     </row>
     <row r="16" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="14" t="s">
         <v>50</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="J16" s="14" t="s">
         <v>98</v>
       </c>
       <c r="K16" s="2" t="s">
@@ -6212,13 +6301,13 @@
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="14" t="s">
         <v>52</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="J17" s="14" t="s">
         <v>145</v>
       </c>
       <c r="K17" s="2" t="s">
@@ -6227,13 +6316,13 @@
       <c r="N17" s="7"/>
     </row>
     <row r="18" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="14" t="s">
         <v>54</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" s="14" t="s">
         <v>146</v>
       </c>
       <c r="K18" s="2" t="s">
@@ -6241,13 +6330,13 @@
       </c>
     </row>
     <row r="19" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="14" t="s">
         <v>56</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="14" t="s">
         <v>147</v>
       </c>
       <c r="K19" s="2" t="s">
@@ -6255,13 +6344,13 @@
       </c>
     </row>
     <row r="20" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="14" t="s">
         <v>58</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="J20" s="15" t="s">
+      <c r="J20" s="14" t="s">
         <v>148</v>
       </c>
       <c r="K20" s="2" t="s">
@@ -6269,7 +6358,7 @@
       </c>
     </row>
     <row r="21" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="14" t="s">
         <v>60</v>
       </c>
       <c r="H21" s="2" t="s">
@@ -6277,7 +6366,7 @@
       </c>
     </row>
     <row r="22" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="14" t="s">
         <v>61</v>
       </c>
       <c r="H22" s="2" t="s">
